--- a/ejemplos/Extornos DEMO.xlsx
+++ b/ejemplos/Extornos DEMO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,10 +450,10 @@
         <v>900001</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46141.4</v>
+        <v>46120.33819444444</v>
       </c>
       <c r="C2" t="n">
-        <v>7194.98</v>
+        <v>2306.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -466,10 +466,10 @@
         <v>900002</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46137.59722222222</v>
+        <v>46135.71597222222</v>
       </c>
       <c r="C3" t="n">
-        <v>6600.46</v>
+        <v>5395.98</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -482,14 +482,14 @@
         <v>900003</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46114.64652777778</v>
+        <v>46135.40902777778</v>
       </c>
       <c r="C4" t="n">
-        <v>850.9400000000001</v>
+        <v>3977.55</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR CLIENTE</t>
         </is>
       </c>
     </row>
@@ -498,10 +498,10 @@
         <v>900004</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46116.39444444444</v>
+        <v>46125.52777777778</v>
       </c>
       <c r="C5" t="n">
-        <v>1783.55</v>
+        <v>5398.97</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -514,14 +514,14 @@
         <v>900005</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46125.48333333333</v>
+        <v>46116.37847222222</v>
       </c>
       <c r="C6" t="n">
-        <v>659.52</v>
+        <v>1415.39</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR SISTEMA</t>
         </is>
       </c>
     </row>
@@ -530,14 +530,14 @@
         <v>900006</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46138.70833333334</v>
+        <v>46150.35902777778</v>
       </c>
       <c r="C7" t="n">
-        <v>7337.32</v>
+        <v>4797.36</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR SISTEMA</t>
         </is>
       </c>
     </row>
@@ -546,10 +546,10 @@
         <v>900007</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46144.70694444444</v>
+        <v>46151.40972222222</v>
       </c>
       <c r="C8" t="n">
-        <v>4456.35</v>
+        <v>4946.59</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -562,14 +562,14 @@
         <v>900008</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46143.39583333334</v>
+        <v>46163.59652777778</v>
       </c>
       <c r="C9" t="n">
-        <v>1213.4</v>
+        <v>4785.67</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERROR CLIENTE</t>
+          <t>ERROR USUARIO</t>
         </is>
       </c>
     </row>
@@ -578,14 +578,14 @@
         <v>900009</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46166.51180555556</v>
+        <v>46145.67430555556</v>
       </c>
       <c r="C10" t="n">
-        <v>2878.92</v>
+        <v>3539.98</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR SISTEMA</t>
         </is>
       </c>
     </row>
@@ -594,14 +594,14 @@
         <v>900010</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46145.70069444444</v>
+        <v>46155.70277777778</v>
       </c>
       <c r="C11" t="n">
-        <v>2848.81</v>
+        <v>4523.13</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ERROR SISTEMA</t>
+          <t>ERROR CLIENTE</t>
         </is>
       </c>
     </row>
@@ -610,14 +610,14 @@
         <v>900011</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46155.53055555555</v>
+        <v>46158.39791666667</v>
       </c>
       <c r="C12" t="n">
-        <v>7879.75</v>
+        <v>6778.58</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR SISTEMA</t>
         </is>
       </c>
     </row>
@@ -626,10 +626,10 @@
         <v>900012</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46200.56875</v>
+        <v>46198.4875</v>
       </c>
       <c r="C13" t="n">
-        <v>1270.58</v>
+        <v>7232.02</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -642,14 +642,14 @@
         <v>900013</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46200.33888888889</v>
+        <v>46193.41666666666</v>
       </c>
       <c r="C14" t="n">
-        <v>1288.52</v>
+        <v>4660.41</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ERROR USUARIO</t>
+          <t>ERROR CLIENTE</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         <v>900014</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46211.42013888889</v>
+        <v>46205.44166666667</v>
       </c>
       <c r="C15" t="n">
-        <v>1933.7</v>
+        <v>2046.72</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ERROR CLIENTE</t>
+          <t>ERROR USUARIO</t>
         </is>
       </c>
     </row>
@@ -674,14 +674,14 @@
         <v>900015</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46215.66666666666</v>
+        <v>46221.5375</v>
       </c>
       <c r="C16" t="n">
-        <v>7505.83</v>
+        <v>6148.02</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ERROR CLIENTE</t>
+          <t>ERROR USUARIO</t>
         </is>
       </c>
     </row>
@@ -690,10 +690,10 @@
         <v>900016</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46212.33819444444</v>
+        <v>46251.51597222222</v>
       </c>
       <c r="C17" t="n">
-        <v>860.03</v>
+        <v>7747.07</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -706,30 +706,14 @@
         <v>900017</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46212.57222222222</v>
+        <v>46265.34375</v>
       </c>
       <c r="C18" t="n">
-        <v>5095.63</v>
+        <v>2754.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>ERROR CLIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>900018</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46212.45763888889</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1533.22</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ERROR USUARIO</t>
         </is>
       </c>
     </row>
